--- a/marketing_forms/003_publishing_book_fair_lead_generation--marketing_forms.xlsx
+++ b/marketing_forms/003_publishing_book_fair_lead_generation--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1398,34 +1398,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>lead_source_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Web</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>lead_source_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>jim</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1437,46 +1437,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lead_source_choices</t>
+          <t>lead_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lead_source_choices</t>
+          <t>lead_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>existing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Existing</t>
         </is>
       </c>
     </row>
@@ -1488,46 +1488,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>qualified</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Qualified</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>lead_status_choices</t>
+          <t>lead_category_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>literary</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Literary</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lead_status_choices</t>
+          <t>lead_category_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qualified</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qualified</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1539,46 +1539,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>literary</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Literary</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>lead_category_choices</t>
+          <t>event_time_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>am</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>lead_category_choices</t>
+          <t>event_time_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>pm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>PM</t>
         </is>
       </c>
     </row>
@@ -1590,46 +1590,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>all_day</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>All Day</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>event_time_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pm</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>event_time_choices</t>
+          <t>event_type_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>all_day</t>
+          <t>seminar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>All Day</t>
+          <t>Seminar</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>conference</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -1658,46 +1658,46 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>seminar</t>
+          <t>book_fair</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seminar</t>
+          <t>Book Fair</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>lead_qualifier_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>workshop</t>
+          <t>publishing_team</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Publishing Team</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>lead_qualifier_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>book_fair</t>
+          <t>author</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Book Fair</t>
+          <t>Author</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>publishing_team</t>
+          <t>editor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Publishing Team</t>
+          <t>Editor</t>
         </is>
       </c>
     </row>
@@ -1726,46 +1726,46 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>designer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>Designer</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>lead_qualifier_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>editor</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lead_qualifier_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>designer</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>phone_call</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phone Call</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
@@ -1794,46 +1794,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>follow_up_method_choices</t>
+          <t>event_size_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Text Message</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>follow_up_method_choices</t>
+          <t>event_size_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>in_person</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>In Person</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1845,46 +1845,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>event_size_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>event_size_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>followed-up</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Followed-up</t>
         </is>
       </c>
     </row>
@@ -1896,44 +1896,10 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>no_follow-up</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>followed-up</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Followed-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no_follow-up</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
         <is>
           <t>No Follow-up</t>
         </is>
